--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week05/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>סתיו שמש – היופי שבאמצע⁩</v>
+        <v>אור קודאי – פירורים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-29</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%aa%d7%99%d7%95-%d7%a9%d7%9e%d7%a9-%d7%94%d7%99%d7%95%d7%a4%d7%99-%d7%a9%d7%91%d7%90%d7%9e%d7%a6%d7%a2%e2%81%a9/</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%a8-%d7%a7%d7%95%d7%93%d7%90%d7%99-%d7%a4%d7%99%d7%a8%d7%95%d7%a8%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-29</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"היופי שבאמצע” של סתיו שמש הוא שיר שמנסה לתאר מצב נפשי מאוד עכשווי: חיים בתוך געגוע מתמשך  לא רק לאדם אחר, אלא לגרסאות קודמות של עצמנו, שיר על זיכרון רגשי, על פצע שלא נעלם אלא מחליף צורה, ועל הניסיון ללמוד</v>
+        <v>אור קודאי שר בלדה מלנכולית שנשענת פחות על עלילה ויותר על תחושה – תחושת ריקנות אחרי אהבה שנשחקה עד שלא נותר ממנה כמעט דבר. הדימוי "פירורים" מבטא לא שברון לב דרמטי, אלא שאריות. של משהו שהיה פעם שלם, חם ומזין,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>סתיו שמש – היופי שבאמצע⁩</v>
+        <v>אור קודאי – פירורים</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week05/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אור קודאי – פירורים</v>
+        <v>איתי עברון – בא מלמטה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%a8-%d7%a7%d7%95%d7%93%d7%90%d7%99-%d7%a4%d7%99%d7%a8%d7%95%d7%a8%d7%99%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%90%d7%99%d7%aa%d7%99-%d7%a2%d7%91%d7%a8%d7%95%d7%9f-%d7%91%d7%90-%d7%9e%d7%9c%d7%9e%d7%98%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>אור קודאי שר בלדה מלנכולית שנשענת פחות על עלילה ויותר על תחושה – תחושת ריקנות אחרי אהבה שנשחקה עד שלא נותר ממנה כמעט דבר. הדימוי "פירורים" מבטא לא שברון לב דרמטי, אלא שאריות. של משהו שהיה פעם שלם, חם ומזין,</v>
+        <v>"בא מלמטה" של איתי עברון  הוא שיר רוק קברטי-תיאטרלי שמציג דיוקן עצמי חסר מעצורים של אמן צעיר הנאבק בין הצורך להתקבל לבין הדחף להיות נאמן לאש הפנימית שלו. זהו שיר על זהות, מעמד, שאפתנות ועל הסירוב להתנצל על מי שאתה.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אור קודאי – פירורים</v>
+        <v>איתי עברון – בא מלמטה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week05/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>איתי עברון – בא מלמטה</v>
+        <v>ארקדי דוכין – תנו לבלון לעוף</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-31</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%99%d7%aa%d7%99-%d7%a2%d7%91%d7%a8%d7%95%d7%9f-%d7%91%d7%90-%d7%9e%d7%9c%d7%9e%d7%98%d7%94/</v>
+        <v>https://yosmusic.com/%d7%90%d7%a8%d7%a7%d7%93%d7%99-%d7%93%d7%95%d7%9b%d7%99%d7%9f-%d7%aa%d7%a0%d7%95-%d7%9c%d7%91%d7%9c%d7%95%d7%9f-%d7%9c%d7%a2%d7%95%d7%a3/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-31</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"בא מלמטה" של איתי עברון  הוא שיר רוק קברטי-תיאטרלי שמציג דיוקן עצמי חסר מעצורים של אמן צעיר הנאבק בין הצורך להתקבל לבין הדחף להיות נאמן לאש הפנימית שלו. זהו שיר על זהות, מעמד, שאפתנות ועל הסירוב להתנצל על מי שאתה.</v>
+        <v>הטריגר לכתיבה היה סיפור קטן ואמיתי שארקדי דוכין לא הצליח להשתחרר ממנו: השיר נכתב בעקבות הרצח המטלטל של ימנו (בנימין) זלקה ז״ל. אבל זה לא שיר על הרצח. זה שיר על טוב לב. הטריגר לכתיבה היה סיפור קטן ואמיתי שארקדי</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>איתי עברון – בא מלמטה</v>
+        <v>ארקדי דוכין – תנו לבלון לעוף</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week05/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ארקדי דוכין – תנו לבלון לעוף</v>
+        <v>יובל דיין – לא להרגיש כלל</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-31</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%a8%d7%a7%d7%93%d7%99-%d7%93%d7%95%d7%9b%d7%99%d7%9f-%d7%aa%d7%a0%d7%95-%d7%9c%d7%91%d7%9c%d7%95%d7%9f-%d7%9c%d7%a2%d7%95%d7%a3/</v>
+        <v>https://yosmusic.com/%d7%99%d7%95%d7%91%d7%9c-%d7%93%d7%99%d7%99%d7%9f-%d7%9c%d7%90-%d7%9c%d7%94%d7%a8%d7%92%d7%99%d7%a9-%d7%9b%d7%9c%d7%9c/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-31</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הטריגר לכתיבה היה סיפור קטן ואמיתי שארקדי דוכין לא הצליח להשתחרר ממנו: השיר נכתב בעקבות הרצח המטלטל של ימנו (בנימין) זלקה ז״ל. אבל זה לא שיר על הרצח. זה שיר על טוב לב. הטריגר לכתיבה היה סיפור קטן ואמיתי שארקדי</v>
+        <v>"לא להרגיש כלל" הוא שיר שעוסק במנגנוני הימנעות רגשיים – הרצון לברוח מכאב, חרדה ועצב במקום להתמודד איתם. מה שמעניין בו הוא שהמילים והמוזיקה פועלות בכיוונים משלימים: הטקסט מתאר הכחשה ובריחה, בעוד שהלחן והביצוע של יובל דיין מעניקים לשיר תחושה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ארקדי דוכין – תנו לבלון לעוף</v>
+        <v>יובל דיין – לא להרגיש כלל</v>
       </c>
     </row>
   </sheetData>
